--- a/output/full_scan/batch_seq1_2026-06-24.xlsx
+++ b/output/full_scan/batch_seq1_2026-06-24.xlsx
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-3.645828043239471</v>
+        <v>-3.645828043239472</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
